--- a/artfynd/A 24507-2024 artfynd.xlsx
+++ b/artfynd/A 24507-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118676110</v>
+        <v>118676109</v>
       </c>
       <c r="B5" t="n">
-        <v>78221</v>
+        <v>79073</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1055,7 +1055,7 @@
         <v>367157</v>
       </c>
       <c r="R5" t="n">
-        <v>6857646</v>
+        <v>6857645</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118676109</v>
+        <v>118676110</v>
       </c>
       <c r="B7" t="n">
-        <v>79073</v>
+        <v>78221</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1277,7 +1277,7 @@
         <v>367157</v>
       </c>
       <c r="R7" t="n">
-        <v>6857645</v>
+        <v>6857646</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>

--- a/artfynd/A 24507-2024 artfynd.xlsx
+++ b/artfynd/A 24507-2024 artfynd.xlsx
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118676109</v>
+        <v>118676111</v>
       </c>
       <c r="B5" t="n">
-        <v>79073</v>
+        <v>78220</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1024,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1052,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>367157</v>
+        <v>367160</v>
       </c>
       <c r="R5" t="n">
-        <v>6857645</v>
+        <v>6857644</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118676108</v>
+        <v>118676110</v>
       </c>
       <c r="B6" t="n">
-        <v>78129</v>
+        <v>78221</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>367296</v>
+        <v>367157</v>
       </c>
       <c r="R6" t="n">
-        <v>6857598</v>
+        <v>6857646</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118676110</v>
+        <v>118676109</v>
       </c>
       <c r="B7" t="n">
-        <v>78221</v>
+        <v>79073</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1277,7 +1277,7 @@
         <v>367157</v>
       </c>
       <c r="R7" t="n">
-        <v>6857646</v>
+        <v>6857645</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118676111</v>
+        <v>118676108</v>
       </c>
       <c r="B8" t="n">
-        <v>78220</v>
+        <v>78129</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>367160</v>
+        <v>367296</v>
       </c>
       <c r="R8" t="n">
-        <v>6857644</v>
+        <v>6857598</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 24507-2024 artfynd.xlsx
+++ b/artfynd/A 24507-2024 artfynd.xlsx
@@ -1011,7 +1011,7 @@
         <v>118676111</v>
       </c>
       <c r="B5" t="n">
-        <v>78220</v>
+        <v>78227</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1119,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118676110</v>
+        <v>118676108</v>
       </c>
       <c r="B6" t="n">
-        <v>78221</v>
+        <v>78136</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,21 +1135,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>367157</v>
+        <v>367296</v>
       </c>
       <c r="R6" t="n">
-        <v>6857646</v>
+        <v>6857598</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,7 +1233,7 @@
         <v>118676109</v>
       </c>
       <c r="B7" t="n">
-        <v>79073</v>
+        <v>79080</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118676108</v>
+        <v>118676110</v>
       </c>
       <c r="B8" t="n">
-        <v>78129</v>
+        <v>78228</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1385,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>367296</v>
+        <v>367157</v>
       </c>
       <c r="R8" t="n">
-        <v>6857598</v>
+        <v>6857646</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>

--- a/artfynd/A 24507-2024 artfynd.xlsx
+++ b/artfynd/A 24507-2024 artfynd.xlsx
@@ -1230,10 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118676109</v>
+        <v>118676110</v>
       </c>
       <c r="B7" t="n">
-        <v>79080</v>
+        <v>78228</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1277,7 +1277,7 @@
         <v>367157</v>
       </c>
       <c r="R7" t="n">
-        <v>6857645</v>
+        <v>6857646</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1341,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118676110</v>
+        <v>118676109</v>
       </c>
       <c r="B8" t="n">
-        <v>78228</v>
+        <v>79080</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,21 +1357,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1388,7 +1388,7 @@
         <v>367157</v>
       </c>
       <c r="R8" t="n">
-        <v>6857646</v>
+        <v>6857645</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
